--- a/data_qr/2026-05-9.xlsx
+++ b/data_qr/2026-05-9.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\Desktop\my_first_website\data_qr\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -634,560 +634,560 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C1:G34"/>
+  <dimension ref="B1:F34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="19.42578125" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375"/>
-    <col min="11" max="11" width="11.7109375"/>
-    <col min="13" max="13" width="11.7109375"/>
+    <col min="2" max="2" width="19.42578125" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" customWidth="1"/>
+    <col min="4" max="4" width="17.28515625" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375"/>
+    <col min="10" max="10" width="11.7109375"/>
+    <col min="12" max="12" width="11.7109375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:7" ht="15.75">
-      <c r="C1" s="15" t="s">
-        <v>0</v>
-      </c>
+    <row r="1" spans="2:6" ht="15.75">
+      <c r="B1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="15"/>
       <c r="D1" s="15"/>
       <c r="E1" s="15"/>
       <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-    </row>
-    <row r="2" spans="3:7" ht="15.75">
-      <c r="C2" s="15" t="s">
+    </row>
+    <row r="2" spans="2:6" ht="15.75">
+      <c r="B2" s="15" t="s">
         <v>1</v>
       </c>
+      <c r="C2" s="15"/>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-    </row>
-    <row r="3" spans="3:7" ht="15.75">
-      <c r="C3" s="16">
+    </row>
+    <row r="3" spans="2:6" ht="15.75">
+      <c r="B3" s="16">
         <v>46151</v>
       </c>
+      <c r="C3" s="16"/>
       <c r="D3" s="16"/>
       <c r="E3" s="16"/>
       <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-    </row>
-    <row r="4" spans="3:7" ht="14.45" customHeight="1">
-      <c r="C4" s="17" t="s">
+    </row>
+    <row r="4" spans="2:6" ht="14.45" customHeight="1">
+      <c r="B4" s="17" t="s">
         <v>34</v>
       </c>
+      <c r="C4" s="17"/>
       <c r="D4" s="17"/>
       <c r="E4" s="17"/>
       <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-    </row>
-    <row r="5" spans="3:7" ht="14.45" customHeight="1">
-      <c r="C5" s="18"/>
-      <c r="D5" s="18" t="s">
+    </row>
+    <row r="5" spans="2:6" ht="14.45" customHeight="1">
+      <c r="B5" s="18"/>
+      <c r="C5" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18" t="s">
+      <c r="D5" s="18"/>
+      <c r="E5" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="18"/>
-    </row>
-    <row r="6" spans="3:7" ht="16.5">
-      <c r="C6" s="18" t="s">
+      <c r="F5" s="18"/>
+    </row>
+    <row r="6" spans="2:6" ht="16.5">
+      <c r="B6" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="3:7" ht="16.5">
-      <c r="C7" s="4" t="s">
+    <row r="7" spans="2:6" ht="16.5">
+      <c r="B7" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="C7" s="5">
+        <v>18</v>
+      </c>
       <c r="D7" s="5">
+        <v>325320</v>
+      </c>
+      <c r="E7" s="6">
+        <v>16</v>
+      </c>
+      <c r="F7" s="6">
+        <v>120370</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" ht="16.5">
+      <c r="B8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="5">
+        <v>2307</v>
+      </c>
+      <c r="D8" s="5">
+        <v>13630157.32</v>
+      </c>
+      <c r="E8" s="6">
+        <v>398</v>
+      </c>
+      <c r="F8" s="6">
+        <v>7212587.2999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" ht="16.5">
+      <c r="B9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="8">
+        <v>9</v>
+      </c>
+      <c r="D9" s="5">
+        <v>17401</v>
+      </c>
+      <c r="E9" s="6">
+        <v>3</v>
+      </c>
+      <c r="F9" s="6">
+        <v>41587</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" ht="16.5">
+      <c r="B10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="8">
+        <v>20</v>
+      </c>
+      <c r="D10" s="5">
+        <v>4097</v>
+      </c>
+      <c r="E10" s="6">
+        <v>2</v>
+      </c>
+      <c r="F10" s="6">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" ht="16.5">
+      <c r="B11" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="8">
+        <v>15</v>
+      </c>
+      <c r="D11" s="5">
+        <v>3981</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" ht="16.5">
+      <c r="B12" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="9">
+        <v>21</v>
+      </c>
+      <c r="D12" s="5">
+        <v>7584</v>
+      </c>
+      <c r="E12" s="5">
+        <v>4</v>
+      </c>
+      <c r="F12" s="6">
+        <v>135000</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" ht="16.5">
+      <c r="B13" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="5">
+        <v>843</v>
+      </c>
+      <c r="D13" s="5">
+        <v>21231480</v>
+      </c>
+      <c r="E13" s="6">
+        <v>508</v>
+      </c>
+      <c r="F13" s="6">
+        <v>4026140.5</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" ht="16.5">
+      <c r="B14" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="5">
+        <v>153</v>
+      </c>
+      <c r="D14" s="5">
+        <v>189167.91</v>
+      </c>
+      <c r="E14" s="6">
+        <v>17</v>
+      </c>
+      <c r="F14" s="6">
+        <v>12625.99</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" ht="16.5">
+      <c r="B15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="5">
+        <v>74</v>
+      </c>
+      <c r="D15" s="5">
+        <v>1103111</v>
+      </c>
+      <c r="E15" s="6">
+        <v>1</v>
+      </c>
+      <c r="F15" s="6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" ht="16.5">
+      <c r="B16" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="5">
+        <v>454</v>
+      </c>
+      <c r="D16" s="5">
+        <v>4911732.3099999996</v>
+      </c>
+      <c r="E16" s="6">
+        <v>2487</v>
+      </c>
+      <c r="F16" s="6">
+        <v>7186767.29</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" ht="16.5">
+      <c r="B17" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="5">
+        <v>55</v>
+      </c>
+      <c r="D17" s="5">
+        <v>123114.5</v>
+      </c>
+      <c r="E17" s="6">
+        <v>29</v>
+      </c>
+      <c r="F17" s="6">
+        <v>26037.93</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" ht="16.5">
+      <c r="B18" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="5">
-        <v>325320</v>
-      </c>
-      <c r="F7" s="6">
-        <v>16</v>
-      </c>
-      <c r="G7" s="6">
-        <v>120370</v>
-      </c>
-    </row>
-    <row r="8" spans="3:7" ht="16.5">
-      <c r="C8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="5">
-        <v>2307</v>
-      </c>
-      <c r="E8" s="5">
-        <v>13630157.32</v>
-      </c>
-      <c r="F8" s="6">
-        <v>398</v>
-      </c>
-      <c r="G8" s="6">
-        <v>7212587.2999999998</v>
-      </c>
-    </row>
-    <row r="9" spans="3:7" ht="16.5">
-      <c r="C9" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="8">
-        <v>9</v>
-      </c>
-      <c r="E9" s="5">
-        <v>17401</v>
-      </c>
-      <c r="F9" s="6">
-        <v>3</v>
-      </c>
-      <c r="G9" s="6">
-        <v>41587</v>
-      </c>
-    </row>
-    <row r="10" spans="3:7" ht="16.5">
-      <c r="C10" s="7" t="s">
+      <c r="C18" s="5">
+        <v>79</v>
+      </c>
+      <c r="D18" s="5">
+        <v>2058093.87</v>
+      </c>
+      <c r="E18" s="6">
+        <v>314</v>
+      </c>
+      <c r="F18" s="6">
+        <v>16391890.460000001</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" ht="16.5">
+      <c r="B19" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="5">
+        <v>89</v>
+      </c>
+      <c r="D19" s="5">
+        <v>104653.14</v>
+      </c>
+      <c r="E19" s="6">
+        <v>198</v>
+      </c>
+      <c r="F19" s="6">
+        <v>4810734.58</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" ht="16.5">
+      <c r="B20" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="5">
+        <v>4</v>
+      </c>
+      <c r="D20" s="5">
+        <v>15700</v>
+      </c>
+      <c r="E20" s="6">
+        <v>6</v>
+      </c>
+      <c r="F20" s="6">
+        <v>4186</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" ht="16.5">
+      <c r="B21" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="5">
+        <v>1</v>
+      </c>
+      <c r="D21" s="5">
         <v>10</v>
       </c>
-      <c r="D10" s="8">
-        <v>20</v>
-      </c>
-      <c r="E10" s="5">
-        <v>4097</v>
-      </c>
-      <c r="F10" s="6">
+      <c r="E21" s="6">
+        <v>1</v>
+      </c>
+      <c r="F21" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" ht="16.5">
+      <c r="B22" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="5">
+        <v>39</v>
+      </c>
+      <c r="D22" s="5">
+        <v>52350</v>
+      </c>
+      <c r="E22" s="6">
+        <v>77</v>
+      </c>
+      <c r="F22" s="6">
+        <v>2903924</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" ht="16.5">
+      <c r="B23" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+    </row>
+    <row r="24" spans="2:6" ht="16.5">
+      <c r="B24" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+    </row>
+    <row r="25" spans="2:6" ht="16.5">
+      <c r="B25" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="5">
+        <v>474</v>
+      </c>
+      <c r="D25" s="5">
+        <v>418495</v>
+      </c>
+      <c r="E25" s="6">
+        <v>55</v>
+      </c>
+      <c r="F25" s="6">
+        <v>23868</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" ht="16.5">
+      <c r="B26" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" s="10">
+        <v>14</v>
+      </c>
+      <c r="D26" s="5">
+        <v>263986</v>
+      </c>
+      <c r="E26" s="6">
+        <v>12</v>
+      </c>
+      <c r="F26" s="6">
+        <v>423561</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" ht="16.5">
+      <c r="B27" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" s="10">
+        <v>10</v>
+      </c>
+      <c r="D27" s="5">
+        <v>78702</v>
+      </c>
+      <c r="E27" s="6">
+        <v>0</v>
+      </c>
+      <c r="F27" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" ht="16.5">
+      <c r="B28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="10">
+        <v>122</v>
+      </c>
+      <c r="D28" s="5">
+        <v>312445</v>
+      </c>
+      <c r="E28" s="6">
+        <v>0</v>
+      </c>
+      <c r="F28" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" ht="16.5">
+      <c r="B29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C29" s="10">
+        <v>5</v>
+      </c>
+      <c r="D29" s="5">
+        <v>17</v>
+      </c>
+      <c r="E29" s="6">
+        <v>683</v>
+      </c>
+      <c r="F29" s="6">
+        <v>934243</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" ht="16.5">
+      <c r="B30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C30" s="11">
+        <v>0</v>
+      </c>
+      <c r="D30" s="5">
+        <v>0</v>
+      </c>
+      <c r="E30" s="6">
         <v>2</v>
       </c>
-      <c r="G10" s="6">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="11" spans="3:7" ht="16.5">
-      <c r="C11" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="8">
-        <v>15</v>
-      </c>
-      <c r="E11" s="5">
-        <v>3981</v>
-      </c>
-      <c r="F11" s="6">
-        <v>0</v>
-      </c>
-      <c r="G11" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="3:7" ht="16.5">
-      <c r="C12" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="9">
-        <v>21</v>
-      </c>
-      <c r="E12" s="5">
-        <v>7584</v>
-      </c>
-      <c r="F12" s="5">
+      <c r="F30" s="6">
+        <v>79900</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" ht="16.5">
+      <c r="B31" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C31" s="12">
         <v>4</v>
       </c>
-      <c r="G12" s="6">
-        <v>135000</v>
-      </c>
-    </row>
-    <row r="13" spans="3:7" ht="16.5">
-      <c r="C13" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="5">
-        <v>843</v>
-      </c>
-      <c r="E13" s="5">
-        <v>21231480</v>
-      </c>
-      <c r="F13" s="6">
-        <v>508</v>
-      </c>
-      <c r="G13" s="6">
-        <v>4026140.5</v>
-      </c>
-    </row>
-    <row r="14" spans="3:7" ht="16.5">
-      <c r="C14" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="5">
-        <v>153</v>
-      </c>
-      <c r="E14" s="5">
-        <v>189167.91</v>
-      </c>
-      <c r="F14" s="6">
-        <v>17</v>
-      </c>
-      <c r="G14" s="6">
-        <v>12625.99</v>
-      </c>
-    </row>
-    <row r="15" spans="3:7" ht="16.5">
-      <c r="C15" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="5">
-        <v>74</v>
-      </c>
-      <c r="E15" s="5">
-        <v>1103111</v>
-      </c>
-      <c r="F15" s="6">
-        <v>1</v>
-      </c>
-      <c r="G15" s="6">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="3:7" ht="16.5">
-      <c r="C16" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="5">
-        <v>454</v>
-      </c>
-      <c r="E16" s="5">
-        <v>4911732.3099999996</v>
-      </c>
-      <c r="F16" s="6">
-        <v>2487</v>
-      </c>
-      <c r="G16" s="6">
-        <v>7186767.29</v>
-      </c>
-    </row>
-    <row r="17" spans="3:7" ht="16.5">
-      <c r="C17" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" s="5">
-        <v>55</v>
-      </c>
-      <c r="E17" s="5">
-        <v>123114.5</v>
-      </c>
-      <c r="F17" s="6">
-        <v>29</v>
-      </c>
-      <c r="G17" s="6">
-        <v>26037.93</v>
-      </c>
-    </row>
-    <row r="18" spans="3:7" ht="16.5">
-      <c r="C18" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D18" s="5">
-        <v>79</v>
-      </c>
-      <c r="E18" s="5">
-        <v>2058093.87</v>
-      </c>
-      <c r="F18" s="6">
-        <v>314</v>
-      </c>
-      <c r="G18" s="6">
-        <v>16391890.460000001</v>
-      </c>
-    </row>
-    <row r="19" spans="3:7" ht="16.5">
-      <c r="C19" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="5">
-        <v>89</v>
-      </c>
-      <c r="E19" s="5">
-        <v>104653.14</v>
-      </c>
-      <c r="F19" s="6">
-        <v>198</v>
-      </c>
-      <c r="G19" s="6">
-        <v>4810734.58</v>
-      </c>
-    </row>
-    <row r="20" spans="3:7" ht="16.5">
-      <c r="C20" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="5">
-        <v>4</v>
-      </c>
-      <c r="E20" s="5">
-        <v>15700</v>
-      </c>
-      <c r="F20" s="6">
-        <v>6</v>
-      </c>
-      <c r="G20" s="6">
-        <v>4186</v>
-      </c>
-    </row>
-    <row r="21" spans="3:7" ht="16.5">
-      <c r="C21" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="D21" s="5">
-        <v>1</v>
-      </c>
-      <c r="E21" s="5">
-        <v>10</v>
-      </c>
-      <c r="F21" s="6">
-        <v>1</v>
-      </c>
-      <c r="G21" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="3:7" ht="16.5">
-      <c r="C22" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D22" s="5">
-        <v>39</v>
-      </c>
-      <c r="E22" s="5">
-        <v>52350</v>
-      </c>
-      <c r="F22" s="6">
-        <v>77</v>
-      </c>
-      <c r="G22" s="6">
-        <v>2903924</v>
-      </c>
-    </row>
-    <row r="23" spans="3:7" ht="16.5">
-      <c r="C23" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-    </row>
-    <row r="24" spans="3:7" ht="16.5">
-      <c r="C24" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-    </row>
-    <row r="25" spans="3:7" ht="16.5">
-      <c r="C25" s="7" t="s">
+      <c r="D31" s="6">
+        <v>1460</v>
+      </c>
+      <c r="E31" s="6">
+        <v>0</v>
+      </c>
+      <c r="F31" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" ht="16.5">
+      <c r="B32" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0</v>
+      </c>
+      <c r="D32" s="6">
+        <v>0</v>
+      </c>
+      <c r="E32" s="6">
         <v>24</v>
       </c>
-      <c r="D25" s="5">
-        <v>474</v>
-      </c>
-      <c r="E25" s="5">
-        <v>418495</v>
-      </c>
-      <c r="F25" s="6">
-        <v>55</v>
-      </c>
-      <c r="G25" s="6">
-        <v>23868</v>
-      </c>
-    </row>
-    <row r="26" spans="3:7" ht="16.5">
-      <c r="C26" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D26" s="10">
-        <v>14</v>
-      </c>
-      <c r="E26" s="5">
-        <v>263986</v>
-      </c>
-      <c r="F26" s="6">
-        <v>12</v>
-      </c>
-      <c r="G26" s="6">
-        <v>423561</v>
-      </c>
-    </row>
-    <row r="27" spans="3:7" ht="16.5">
-      <c r="C27" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D27" s="10">
-        <v>10</v>
-      </c>
-      <c r="E27" s="5">
-        <v>78702</v>
-      </c>
-      <c r="F27" s="6">
-        <v>0</v>
-      </c>
-      <c r="G27" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:7" ht="16.5">
-      <c r="C28" s="1" t="s">
+      <c r="F32" s="6">
+        <v>790820</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" ht="16.5">
+      <c r="B33" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" s="9">
         <v>27</v>
       </c>
-      <c r="D28" s="10">
-        <v>122</v>
-      </c>
-      <c r="E28" s="5">
-        <v>312445</v>
-      </c>
-      <c r="F28" s="6">
-        <v>0</v>
-      </c>
-      <c r="G28" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="3:7" ht="16.5">
-      <c r="C29" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D29" s="10">
-        <v>5</v>
-      </c>
-      <c r="E29" s="5">
-        <v>17</v>
-      </c>
-      <c r="F29" s="6">
-        <v>683</v>
-      </c>
-      <c r="G29" s="6">
-        <v>934243</v>
-      </c>
-    </row>
-    <row r="30" spans="3:7" ht="16.5">
-      <c r="C30" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D30" s="11">
-        <v>0</v>
-      </c>
-      <c r="E30" s="5">
-        <v>0</v>
-      </c>
-      <c r="F30" s="6">
-        <v>2</v>
-      </c>
-      <c r="G30" s="6">
-        <v>79900</v>
-      </c>
-    </row>
-    <row r="31" spans="3:7" ht="16.5">
-      <c r="C31" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D31" s="12">
-        <v>4</v>
-      </c>
-      <c r="E31" s="6">
-        <v>1460</v>
-      </c>
-      <c r="F31" s="6">
-        <v>0</v>
-      </c>
-      <c r="G31" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="3:7" ht="16.5">
-      <c r="C32" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D32" s="6">
-        <v>0</v>
-      </c>
-      <c r="E32" s="6">
-        <v>0</v>
-      </c>
-      <c r="F32" s="6">
-        <v>24</v>
-      </c>
-      <c r="G32" s="6">
-        <v>790820</v>
-      </c>
-    </row>
-    <row r="33" spans="3:7" ht="16.5">
-      <c r="C33" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D33" s="9">
-        <v>27</v>
-      </c>
-      <c r="E33" s="5">
+      <c r="D33" s="5">
         <v>271471</v>
       </c>
+      <c r="E33" s="6">
+        <v>0</v>
+      </c>
       <c r="F33" s="6">
         <v>0</v>
       </c>
-      <c r="G33" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="3:7" ht="16.5">
-      <c r="C34" s="7" t="s">
+    </row>
+    <row r="34" spans="2:6" ht="16.5">
+      <c r="B34" s="7" t="s">
         <v>33</v>
+      </c>
+      <c r="C34" s="13">
+        <f>SUM(C7:C33)</f>
+        <v>4837</v>
       </c>
       <c r="D34" s="13">
         <f>SUM(D7:D33)</f>
-        <v>4837</v>
+        <v>45124529.049999997</v>
       </c>
       <c r="E34" s="13">
         <f>SUM(E7:E33)</f>
-        <v>45124529.049999997</v>
+        <v>4837</v>
       </c>
       <c r="F34" s="13">
         <f>SUM(F7:F33)</f>
-        <v>4837</v>
-      </c>
-      <c r="G34" s="13">
-        <f>SUM(G7:G33)</f>
         <v>45124529.049999997</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="C9:C34">
-    <sortCondition ref="C8"/>
+  <sortState ref="B9:B34">
+    <sortCondition ref="B8"/>
   </sortState>
   <mergeCells count="7">
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="B5:B6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
